--- a/src/catalogo_simbolos.xlsx
+++ b/src/catalogo_simbolos.xlsx
@@ -3837,12 +3837,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>132</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="3019425" cy="2038350"/>
+    <ext cx="2400300" cy="1685925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="138" name="Image 138" descr="Picture">
@@ -3869,7 +3869,7 @@
       <row>133</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2533650" cy="2047875"/>
+    <ext cx="2781300" cy="1685925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="139" name="Image 139" descr="Picture">
@@ -3896,7 +3896,7 @@
       <row>134</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2914650" cy="2047875"/>
+    <ext cx="3162300" cy="1685925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="140" name="Image 140" descr="Picture">
@@ -3923,7 +3923,7 @@
       <row>135</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="3295650" cy="2047875"/>
+    <ext cx="3543300" cy="1685925"/>
     <pic>
       <nvPicPr>
         <cNvPr id="141" name="Image 141" descr="Picture">
@@ -3945,12 +3945,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>136</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="3676650" cy="2047875"/>
+    <ext cx="1924050" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="142" name="Image 142" descr="Picture">
@@ -3977,7 +3977,7 @@
       <row>137</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1485900" cy="1047750"/>
+    <ext cx="3019425" cy="2038350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="143" name="Image 143" descr="Picture">
@@ -3999,12 +3999,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>138</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2276475" cy="1009650"/>
+    <ext cx="2533650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="144" name="Image 144" descr="Picture">
@@ -4026,12 +4026,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>138</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1466850" cy="771525"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>139</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2914650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="145" name="Image 145" descr="Picture">
@@ -4055,10 +4055,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>139</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2400300" cy="1476375"/>
+      <row>140</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3295650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="146" name="Image 146" descr="Picture">
@@ -4080,12 +4080,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>140</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1885950" cy="1200150"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>141</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3676650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="147" name="Image 147" descr="Picture">
@@ -4109,10 +4109,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>141</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1485900" cy="742950"/>
+      <row>142</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3019425" cy="2038350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="148" name="Image 148" descr="Picture">
@@ -4134,12 +4134,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>142</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1447800" cy="1276350"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>143</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2533650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="149" name="Image 149" descr="Picture">
@@ -4161,12 +4161,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>143</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1409700" cy="876300"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>144</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2914650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="150" name="Image 150" descr="Picture">
@@ -4190,10 +4190,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>144</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1409700" cy="990600"/>
+      <row>145</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3295650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="151" name="Image 151" descr="Picture">
@@ -4215,12 +4215,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>145</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1752600" cy="1657350"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>146</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3676650" cy="2047875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="152" name="Image 152" descr="Picture">
@@ -4244,10 +4244,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>146</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1590675" cy="1038225"/>
+      <row>147</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1485900" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="153" name="Image 153" descr="Picture">
@@ -4271,10 +4271,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>147</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1543050" cy="1085850"/>
+      <row>148</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2276475" cy="1009650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="154" name="Image 154" descr="Picture">
@@ -4296,12 +4296,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>148</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2438400" cy="857250"/>
+    <ext cx="1466850" cy="771525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="155" name="Image 155" descr="Picture">
@@ -4323,12 +4323,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>148</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2438400" cy="857250"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>149</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2400300" cy="1476375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="156" name="Image 156" descr="Picture">
@@ -4352,10 +4352,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>149</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1438275" cy="685800"/>
+      <row>150</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1885950" cy="1200150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="157" name="Image 157" descr="Picture">
@@ -4379,10 +4379,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>150</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1438275" cy="685800"/>
+      <row>151</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1485900" cy="742950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="158" name="Image 158" descr="Picture">
@@ -4404,12 +4404,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>151</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1638300" cy="1162050"/>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>152</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1447800" cy="1276350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="159" name="Image 159" descr="Picture">
@@ -4433,10 +4433,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>152</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2524125" cy="1543050"/>
+      <row>153</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1409700" cy="876300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="160" name="Image 160" descr="Picture">
@@ -4460,10 +4460,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>153</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2524125" cy="1666875"/>
+      <row>154</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1409700" cy="990600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="161" name="Image 161" descr="Picture">
@@ -4485,12 +4485,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>57150</colOff>
-      <row>154</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2905125" cy="1666875"/>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>155</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1752600" cy="1657350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="162" name="Image 162" descr="Picture">
@@ -4512,12 +4512,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>57150</colOff>
-      <row>155</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="3667125" cy="1666875"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>156</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1590675" cy="1038225"/>
     <pic>
       <nvPicPr>
         <cNvPr id="163" name="Image 163" descr="Picture">
@@ -4541,10 +4541,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>156</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2447925" cy="1657350"/>
+      <row>157</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1543050" cy="1085850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="164" name="Image 164" descr="Picture">
@@ -4566,12 +4566,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>57150</colOff>
-      <row>157</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2209800" cy="1666875"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>158</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2438400" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="165" name="Image 165" descr="Picture">
@@ -4593,12 +4593,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>158</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2590800" cy="1666875"/>
+    <ext cx="2438400" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="166" name="Image 166" descr="Picture">
@@ -4620,12 +4620,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>159</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="3352800" cy="1666875"/>
+    <ext cx="1438275" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="167" name="Image 167" descr="Picture">
@@ -4652,7 +4652,7 @@
       <row>160</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2047875" cy="1257300"/>
+    <ext cx="1438275" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="168" name="Image 168" descr="Picture">
@@ -4679,7 +4679,7 @@
       <row>161</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1333500" cy="1409700"/>
+    <ext cx="1638300" cy="1162050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="169" name="Image 169" descr="Picture">
@@ -4701,12 +4701,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>161</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1371600" cy="1504950"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>162</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2524125" cy="1543050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="170" name="Image 170" descr="Picture">
@@ -4728,12 +4728,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>162</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1485900" cy="1247775"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>163</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2524125" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="171" name="Image 171" descr="Picture">
@@ -4755,12 +4755,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>163</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1485900" cy="1247775"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>164</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2905125" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="172" name="Image 172" descr="Picture">
@@ -4782,12 +4782,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>164</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2276475" cy="1466850"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>165</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3667125" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="173" name="Image 173" descr="Picture">
@@ -4811,10 +4811,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>165</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1457325" cy="971550"/>
+      <row>166</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2447925" cy="1657350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="174" name="Image 174" descr="Picture">
@@ -4836,12 +4836,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>166</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1447800" cy="685800"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>167</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2209800" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="175" name="Image 175" descr="Picture">
@@ -4863,12 +4863,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>167</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1733550" cy="1162050"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>168</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2590800" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="176" name="Image 176" descr="Picture">
@@ -4892,10 +4892,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>168</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2419350" cy="1276350"/>
+      <row>169</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="3352800" cy="1666875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="177" name="Image 177" descr="Picture">
@@ -4919,10 +4919,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>169</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2543175" cy="1276350"/>
+      <row>170</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2047875" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="178" name="Image 178" descr="Picture">
@@ -4944,12 +4944,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>57150</colOff>
-      <row>170</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2266950" cy="1285875"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>171</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1333500" cy="1409700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="179" name="Image 179" descr="Picture">
@@ -4971,12 +4971,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>171</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2552700" cy="1285875"/>
+    <ext cx="1371600" cy="1504950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="180" name="Image 180" descr="Picture">
@@ -4998,12 +4998,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>172</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2971800" cy="1285875"/>
+    <ext cx="1485900" cy="1247775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="181" name="Image 181" descr="Picture">
@@ -5025,12 +5025,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>173</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="3314700" cy="1285875"/>
+    <ext cx="1485900" cy="1247775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="182" name="Image 182" descr="Picture">
@@ -5057,7 +5057,7 @@
       <row>174</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1447800" cy="1047750"/>
+    <ext cx="2276475" cy="1466850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="183" name="Image 183" descr="Picture">
@@ -5084,7 +5084,7 @@
       <row>175</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2105025" cy="781050"/>
+    <ext cx="1457325" cy="971550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="184" name="Image 184" descr="Picture">
@@ -5111,7 +5111,7 @@
       <row>176</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1457325" cy="685800"/>
+    <ext cx="1447800" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="185" name="Image 185" descr="Picture">
@@ -5133,12 +5133,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>177</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1362075" cy="1000125"/>
+    <ext cx="1733550" cy="1162050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="186" name="Image 186" descr="Picture">
@@ -5165,7 +5165,7 @@
       <row>178</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1600200" cy="1000125"/>
+    <ext cx="2419350" cy="1276350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="187" name="Image 187" descr="Picture">
@@ -5187,12 +5187,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>179</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2057400" cy="1000125"/>
+    <ext cx="2543175" cy="1276350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="188" name="Image 188" descr="Picture">
@@ -5219,7 +5219,7 @@
       <row>180</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2362200" cy="1000125"/>
+    <ext cx="2266950" cy="1285875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="189" name="Image 189" descr="Picture">
@@ -5241,12 +5241,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>181</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1905000" cy="1638300"/>
+    <ext cx="2552700" cy="1285875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="190" name="Image 190" descr="Picture">
@@ -5268,12 +5268,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>182</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1381125" cy="781050"/>
+    <ext cx="2971800" cy="1285875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="191" name="Image 191" descr="Picture">
@@ -5300,7 +5300,7 @@
       <row>183</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1381125" cy="971550"/>
+    <ext cx="3314700" cy="1285875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="192" name="Image 192" descr="Picture">
@@ -5322,12 +5322,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>184</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1762125" cy="971550"/>
+    <ext cx="1447800" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="193" name="Image 193" descr="Picture">
@@ -5349,12 +5349,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>185</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2143125" cy="971550"/>
+    <ext cx="2105025" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="194" name="Image 194" descr="Picture">
@@ -5376,12 +5376,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>1</col>
       <colOff>57150</colOff>
       <row>186</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2524125" cy="971550"/>
+    <ext cx="1457325" cy="685800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="195" name="Image 195" descr="Picture">
@@ -5403,12 +5403,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>187</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1419225" cy="695325"/>
+    <ext cx="1362075" cy="1000125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="196" name="Image 196" descr="Picture">
@@ -5430,12 +5430,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>2</col>
       <colOff>57150</colOff>
       <row>188</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1485900" cy="1600200"/>
+    <ext cx="1600200" cy="1000125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="197" name="Image 197" descr="Picture">
@@ -5457,12 +5457,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>188</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1485900" cy="1276350"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>189</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2057400" cy="1000125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="198" name="Image 198" descr="Picture">
@@ -5484,12 +5484,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>189</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1905000" cy="1866900"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>190</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2362200" cy="1000125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="199" name="Image 199" descr="Picture">
@@ -5511,12 +5511,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>190</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1924050" cy="1162050"/>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>191</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1905000" cy="1638300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="200" name="Image 200" descr="Picture">
@@ -5538,12 +5538,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>2</col>
-      <colOff>57150</colOff>
-      <row>191</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2209800" cy="1276350"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>192</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1381125" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="201" name="Image 201" descr="Picture">
@@ -5565,12 +5565,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>192</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1590675" cy="1371600"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>193</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1381125" cy="971550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="202" name="Image 202" descr="Picture">
@@ -5592,12 +5592,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>193</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1990725" cy="1276350"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>194</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1762125" cy="971550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="203" name="Image 203" descr="Picture">
@@ -5621,10 +5621,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>194</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2419350" cy="1276350"/>
+      <row>195</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2143125" cy="971550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="204" name="Image 204" descr="Picture">
@@ -5648,10 +5648,10 @@
     <from>
       <col>2</col>
       <colOff>57150</colOff>
-      <row>195</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="2800350" cy="1276350"/>
+      <row>196</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2524125" cy="971550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="205" name="Image 205" descr="Picture">
@@ -5673,12 +5673,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>196</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1533525" cy="1771650"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>197</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1419225" cy="695325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="206" name="Image 206" descr="Picture">
@@ -5702,10 +5702,10 @@
     <from>
       <col>1</col>
       <colOff>57150</colOff>
-      <row>197</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1657350" cy="762000"/>
+      <row>198</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1485900" cy="1600200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="207" name="Image 207" descr="Picture">
@@ -5732,7 +5732,7 @@
       <row>198</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="2495550" cy="819150"/>
+    <ext cx="1485900" cy="1276350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="208" name="Image 208" descr="Picture">
@@ -5754,12 +5754,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>3</col>
       <colOff>57150</colOff>
       <row>199</row>
       <rowOff>190500</rowOff>
     </from>
-    <ext cx="1828800" cy="933450"/>
+    <ext cx="1905000" cy="1866900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="209" name="Image 209" descr="Picture">
@@ -5781,12 +5781,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>3</col>
-      <colOff>57150</colOff>
-      <row>199</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1543050" cy="1066800"/>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>200</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1924050" cy="1162050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="210" name="Image 210" descr="Picture">
@@ -5808,12 +5808,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>57150</colOff>
-      <row>200</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1590675" cy="1371600"/>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>201</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2209800" cy="1276350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="211" name="Image 211" descr="Picture">
@@ -5823,6 +5823,276 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>202</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1590675" cy="1371600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="212" name="Image 212" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg211"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>203</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1990725" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="213" name="Image 213" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg212"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>204</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2419350" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="214" name="Image 214" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg213"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>57150</colOff>
+      <row>205</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2800350" cy="1276350"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="215" name="Image 215" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg214"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>206</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1533525" cy="1771650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="216" name="Image 216" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg215"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>207</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1657350" cy="762000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="217" name="Image 217" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg216"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>208</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="2495550" cy="819150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="218" name="Image 218" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg217"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>209</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1828800" cy="933450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="219" name="Image 219" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg218"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>57150</colOff>
+      <row>209</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1543050" cy="1066800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="220" name="Image 220" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg219"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>57150</colOff>
+      <row>210</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1590675" cy="1371600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="221" name="Image 221" descr="Picture">
+          <a:hlinkClick xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdSvg220"/>
+        </cNvPr>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -6125,7 +6395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7694,923 +7964,1043 @@
     <row r="127" ht="152.25" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>MCCB DRAWOUT</t>
+          <t>MCCB BASIC</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>291_E_LV_SLD_IEC60617_mccb_drawout.svg</t>
+          <t>291_E_LV_SLD_IEC60617_mccb_basic.svg</t>
         </is>
       </c>
     </row>
     <row r="128" ht="153.75" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>MCCB DRAWOUT 1P</t>
+          <t>MCCB BASIC 1P</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>291_E_LV_MLD_IEC60617_mccb_drawout_1p.svg</t>
+          <t>291_E_LV_MLD_IEC60617_mccb_basic_1p.svg</t>
         </is>
       </c>
     </row>
     <row r="129" ht="153.75" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MCCB DRAWOUT 2P</t>
+          <t>MCCB BASIC 2P</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>291_E_LV_MLD_IEC60617_mccb_drawout_2p.svg</t>
+          <t>291_E_LV_MLD_IEC60617_mccb_basic_2p.svg</t>
         </is>
       </c>
     </row>
     <row r="130" ht="153.75" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>MCCB DRAWOUT 3P</t>
+          <t>MCCB BASIC 3P</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>291_E_LV_MLD_IEC60617_mccb_drawout_3p.svg</t>
+          <t>291_E_LV_MLD_IEC60617_mccb_basic_3p.svg</t>
         </is>
       </c>
     </row>
     <row r="131" ht="153.75" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>MCCB DRAWOUT 4P</t>
+          <t>MCCB BASIC 4P</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>291_E_LV_MLD_IEC60617_mccb_drawout_4p.svg</t>
+          <t>291_E_LV_MLD_IEC60617_mccb_basic_4p.svg</t>
         </is>
       </c>
     </row>
     <row r="132" ht="152.25" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>MCCB DRAWOUT</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_mccb_drawout.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="153.75" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>MCCB DRAWOUT 1P</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_drawout_1p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="153.75" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>MCCB DRAWOUT 2P</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_drawout_2p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="153.75" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>MCCB DRAWOUT 3P</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_drawout_3p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="153.75" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>MCCB DRAWOUT 4P</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_drawout_4p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="152.25" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
           <t>MCCB LSIG DRAWOUT</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_mccb_lsig_drawout.svg</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="181.5" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="138" ht="181.5" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>MCCB MOTORIZED</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_mccb_motorized.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="182.25" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>MCCB MOTORIZED 1P</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_motorized_1p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="182.25" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>MCCB MOTORIZED 2P</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_motorized_2p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="182.25" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>MCCB MOTORIZED 3P</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_motorized_3p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="182.25" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>MCCB MOTORIZED 4P</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_mccb_motorized_4p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="181.5" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>MCCB MOTORIZED DRAWOUT</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_mccb_motorized_drawout.svg</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="182.25" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="144" ht="182.25" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>MCCB MOTORIZED DRAWOUT 1P</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_mccb_motorized_drawout_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="182.25" customHeight="1">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="145" ht="182.25" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>MCCB MOTORIZED DRAWOUT 2P</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_mccb_motorized_drawout_2p.svg</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="182.25" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="146" ht="182.25" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>MCCB MOTORIZED DRAWOUT 3P</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_mccb_motorized_drawout_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="182.25" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="147" ht="182.25" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>MCCB MOTORIZED DRAWOUT 4P</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C147" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_mccb_motorized_drawout_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="103.5" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="148" ht="103.5" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>MOTOR 1PH</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_motor_1ph.svg</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="100.5" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="149" ht="100.5" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>MOTOR 3PH</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B149" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_motor_3ph.svg</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_motor_3ph.svg</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="137.25" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="150" ht="137.25" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>MOTOR 3PH 3P</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_motor_3ph_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="115.5" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="151" ht="115.5" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>MOTOR STARTER DOL</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_motor_starter_dol.svg</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="79.5" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="152" ht="79.5" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>NETWORK ANALYZER AR</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B152" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_network_analyzer_ar.svg</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="121.5" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="153" ht="121.5" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>NEUTRAL EARTHING RESISTOR</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_neutral_earthing_resistor.svg</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="90" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="154" ht="90" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>NEUTRAL LINK</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_neutral_link.svg</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="99" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="155" ht="99" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>NEUTRAL LINK 1P</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C155" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_neutral_link_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="151.5" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="156" ht="151.5" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>PETERSEN COIL</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_petersen_coil.svg</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="102.75" customHeight="1">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="157" ht="102.75" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>PF METER</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B157" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_pf_meter.svg</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="106.5" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="158" ht="106.5" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>PILOT LAMP</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_pilot_lamp.svg</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="88.5" customHeight="1">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="159" ht="88.5" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>PROTECTION RELAY</t>
         </is>
       </c>
-      <c r="B149" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_protection_relay.svg</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_protection_relay.svg</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="75" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="160" ht="75" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>PUSHBUTTON NC</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_pushbutton_nc.svg</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="75" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="161" ht="75" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>PUSHBUTTON NO</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr">
+      <c r="B161" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_pushbutton_no.svg</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="112.5" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="162" ht="112.5" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>PV MODULE</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_pv_module.svg</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="142.5" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="163" ht="142.5" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>RCBO</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_rcbo.svg</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="152.25" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="164" ht="152.25" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>RCBO 1P</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rcbo_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="152.25" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="165" ht="152.25" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>RCBO 2P</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C165" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rcbo_2p.svg</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="152.25" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="166" ht="152.25" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>RCBO 4P</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rcbo_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="151.5" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="167" ht="151.5" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>RCCB</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_rccb.svg</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="152.25" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="168" ht="152.25" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>RCCB 1P</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rccb_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="152.25" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="169" ht="152.25" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>RCCB 2P</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C169" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rccb_2p.svg</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="152.25" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="170" ht="152.25" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>RCCB 4P</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C170" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_rccb_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="120" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="171" ht="120" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>RCD RELAY TOROID</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr">
+      <c r="B171" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_rcd_relay_toroid.svg</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="139.5" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="172" ht="139.5" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>REACTOR</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B172" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_reactor.svg</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_reactor.svg</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="119.25" customHeight="1">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="173" ht="119.25" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>RECLOSER</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_recloser.svg</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="119.25" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="174" ht="119.25" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>RECTIFIER</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_rectifier.svg</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="136.5" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="175" ht="136.5" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>RING MAIN UNIT</t>
         </is>
       </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_ring_main_unit.svg</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="97.5" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="176" ht="97.5" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>SELECTOR SWITCH</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_selector_switch.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="75" customHeight="1">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>SOCKET OUTLET</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_SLD_IEC60617_socket_outlet.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="112.5" customHeight="1">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>SOFT STARTER</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_SLD_IEC60617_soft_starter.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="121.5" customHeight="1">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>SOFT STARTER 3P</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_MLD_IEC60617_soft_starter_3p.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="121.5" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>SPD VARISTOR</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_SLD_IEC60617_spd_varistor.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="122.25" customHeight="1">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>SPD VARISTOR 1P</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_MLD_IEC60617_spd_varistor_1p.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="122.25" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>SPD VARISTOR 2P</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_MLD_IEC60617_spd_varistor_2p.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="122.25" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>SPD VARISTOR 3P</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_MLD_IEC60617_spd_varistor_3p.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="122.25" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>SPD VARISTOR 4P</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_MLD_IEC60617_spd_varistor_4p.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="103.5" customHeight="1">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>SURGE ARRESTER</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>291_E_MV_SLD_IEC60617_surge_arrester.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="82.5" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>SWITCH 3WAY</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>291_E_LV_SLD_IEC60617_switch_3way.svg</t>
         </is>
       </c>
     </row>
     <row r="177" ht="75" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
+          <t>SOCKET OUTLET</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_socket_outlet.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="112.5" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>SOFT STARTER</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_soft_starter.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="121.5" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>SOFT STARTER 3P</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_soft_starter_3p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="121.5" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>SPD VARISTOR</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_spd_varistor.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="122.25" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>SPD VARISTOR 1P</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_spd_varistor_1p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="122.25" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>SPD VARISTOR 2P</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_spd_varistor_2p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="122.25" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>SPD VARISTOR 3P</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_spd_varistor_3p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="122.25" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>SPD VARISTOR 4P</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_MLD_IEC60617_spd_varistor_4p.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="103.5" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>SURGE ARRESTER</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>291_E_MV_SLD_IEC60617_surge_arrester.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="82.5" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>SWITCH 3WAY</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>291_E_LV_SLD_IEC60617_switch_3way.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="75" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
           <t>SWITCH DISCONNECTOR</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_switch_disconnector.svg</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="99.75" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="188" ht="99.75" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>SWITCH DISCONNECTOR 1P</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C188" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_switch_disconnector_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="99.75" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="189" ht="99.75" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>SWITCH DISCONNECTOR 2P</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_switch_disconnector_2p.svg</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="99.75" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="190" ht="99.75" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>SWITCH DISCONNECTOR 3P</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_switch_disconnector_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="99.75" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="191" ht="99.75" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>SWITCH DISCONNECTOR 4P</t>
         </is>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_switch_disconnector_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="150" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="192" ht="150" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>SWITCH FUSE COMBINATION</t>
         </is>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_switch_fuse_combination.svg</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="82.5" customHeight="1">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="193" ht="82.5" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>THERMAL OVERLOAD</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B193" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_thermal_overload.svg</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="97.5" customHeight="1">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="194" ht="97.5" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>THERMAL OVERLOAD 1P</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_thermal_overload_1p.svg</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="97.5" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="195" ht="97.5" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>THERMAL OVERLOAD 2P</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_thermal_overload_2p.svg</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="97.5" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="196" ht="97.5" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>THERMAL OVERLOAD 3P</t>
         </is>
       </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_thermal_overload_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="97.5" customHeight="1">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="197" ht="97.5" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>THERMAL OVERLOAD 4P</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C197" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_thermal_overload_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="75.75" customHeight="1">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="198" ht="75.75" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>THREE PHASE MARKER</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_three_phase_marker.svg</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="147" customHeight="1">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="199" ht="147" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>TRANSFORMER 2W</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B199" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_transformer_2w.svg</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_transformer_2w.svg</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="168" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="200" ht="168" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>TRANSFORMER 3W</t>
         </is>
       </c>
-      <c r="D190" s="3" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_transformer_3w.svg</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="112.5" customHeight="1">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="201" ht="112.5" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>UPS</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B201" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_ups.svg</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="121.5" customHeight="1">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="202" ht="121.5" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>UPS 3P</t>
         </is>
       </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_ups_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="129" customHeight="1">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="203" ht="129" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>VARIMETER</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_varimeter.svg</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="121.5" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="204" ht="121.5" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>VFD</t>
         </is>
       </c>
-      <c r="B194" s="3" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_vfd.svg</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="121.5" customHeight="1">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="205" ht="121.5" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>VFD 3P</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_vfd_3p.svg</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="121.5" customHeight="1">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="206" ht="121.5" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>VFD 4P</t>
         </is>
       </c>
-      <c r="C196" s="3" t="inlineStr">
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_MLD_IEC60617_vfd_4p.svg</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="160.5" customHeight="1">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="207" ht="160.5" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>VOLTAGE REGULATOR</t>
         </is>
       </c>
-      <c r="D197" s="3" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_voltage_regulator.svg</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="81" customHeight="1">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="208" ht="81" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>VOLTMETER</t>
         </is>
       </c>
-      <c r="B198" s="3" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_voltmeter.svg</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="85.5" customHeight="1">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="209" ht="85.5" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>VPIS</t>
         </is>
       </c>
-      <c r="D199" s="3" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_vpis.svg</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="105" customHeight="1">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="210" ht="105" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>VT</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_vt.svg</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>291_E_MV_SLD_IEC60617_vt.svg</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="129" customHeight="1">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="211" ht="129" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>WATTMETER</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>291_E_LV_SLD_IEC60617_wattmeter.svg</t>
         </is>
@@ -8755,82 +9145,92 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B208" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B210" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B211" r:id="rId221"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId212"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId222"/>
 </worksheet>
 </file>